--- a/www/flightdata/xlsx/eoss-341.xlsx
+++ b/www/flightdata/xlsx/eoss-341.xlsx
@@ -3384,7 +3384,7 @@
         <v>25859.54</v>
       </c>
       <c r="I2">
-        <v>601</v>
+        <v>427</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
